--- a/Team-Data/2008-09/11-25-2008-09.xlsx
+++ b/Team-Data/2008-09/11-25-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>10</v>
@@ -748,7 +815,7 @@
         <v>5</v>
       </c>
       <c r="AG2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH2" t="n">
         <v>20</v>
@@ -760,7 +827,7 @@
         <v>16</v>
       </c>
       <c r="AK2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL2" t="n">
         <v>2</v>
@@ -775,13 +842,13 @@
         <v>19</v>
       </c>
       <c r="AP2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
         <v>28</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS2" t="n">
         <v>21</v>
@@ -790,28 +857,28 @@
         <v>15</v>
       </c>
       <c r="AU2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
         <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -843,85 +910,85 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.857</v>
+        <v>0.867</v>
       </c>
       <c r="H3" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J3" t="n">
-        <v>75.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>0.35</v>
+        <v>0.342</v>
       </c>
       <c r="O3" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="P3" t="n">
-        <v>29.4</v>
+        <v>29.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="R3" t="n">
         <v>10.4</v>
       </c>
       <c r="S3" t="n">
-        <v>33.1</v>
+        <v>32.7</v>
       </c>
       <c r="T3" t="n">
-        <v>43.6</v>
+        <v>43.1</v>
       </c>
       <c r="U3" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="V3" t="n">
         <v>16.9</v>
       </c>
       <c r="W3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>97.7</v>
+        <v>97.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,10 +1000,10 @@
         <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -945,13 +1012,13 @@
         <v>6</v>
       </c>
       <c r="AL3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM3" t="n">
         <v>18</v>
       </c>
       <c r="AN3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
         <v>2</v>
@@ -960,19 +1027,19 @@
         <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
         <v>30</v>
@@ -981,7 +1048,7 @@
         <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
         <v>5</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>25</v>
@@ -1139,16 +1206,16 @@
         <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
@@ -1157,13 +1224,13 @@
         <v>29</v>
       </c>
       <c r="AV4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1178,7 +1245,7 @@
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>0.429</v>
+        <v>0.467</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J5" t="n">
-        <v>85.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.423</v>
+        <v>0.428</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.348</v>
+        <v>0.352</v>
       </c>
       <c r="O5" t="n">
-        <v>19.8</v>
+        <v>20.7</v>
       </c>
       <c r="P5" t="n">
-        <v>24.3</v>
+        <v>25.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S5" t="n">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="T5" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U5" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="V5" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="W5" t="n">
         <v>8.9</v>
@@ -1270,58 +1337,58 @@
         <v>5.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4</v>
+        <v>-2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AH5" t="n">
         <v>20</v>
       </c>
       <c r="AI5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="n">
         <v>28</v>
       </c>
       <c r="AL5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AP5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>3</v>
@@ -1330,34 +1397,34 @@
         <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT5" t="n">
         <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
         <v>5</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -1392,88 +1459,88 @@
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.846</v>
+        <v>0.769</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>37.8</v>
+        <v>36.4</v>
       </c>
       <c r="J6" t="n">
-        <v>78.5</v>
+        <v>76.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0.482</v>
+        <v>0.474</v>
       </c>
       <c r="L6" t="n">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="M6" t="n">
-        <v>20.5</v>
+        <v>19.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0.352</v>
+        <v>0.349</v>
       </c>
       <c r="O6" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="P6" t="n">
-        <v>26.7</v>
+        <v>27.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="R6" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="T6" t="n">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="U6" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>12.3</v>
+        <v>13.3</v>
       </c>
       <c r="W6" t="n">
         <v>7.5</v>
       </c>
       <c r="X6" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>103.8</v>
+        <v>101.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG6" t="n">
         <v>3</v>
@@ -1482,64 +1549,64 @@
         <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AM6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU6" t="n">
         <v>18</v>
       </c>
-      <c r="AU6" t="n">
-        <v>12</v>
-      </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
         <v>15</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>2</v>
       </c>
       <c r="AZ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA6" t="n">
         <v>9</v>
       </c>
-      <c r="BA6" t="n">
-        <v>14</v>
-      </c>
       <c r="BB6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -1571,94 +1638,94 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.462</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>36.9</v>
+        <v>36.5</v>
       </c>
       <c r="J7" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.437</v>
+        <v>0.433</v>
       </c>
       <c r="L7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="M7" t="n">
         <v>18.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.31</v>
+        <v>0.314</v>
       </c>
       <c r="O7" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="P7" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="Q7" t="n">
         <v>0.79</v>
       </c>
       <c r="R7" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S7" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="T7" t="n">
-        <v>47.3</v>
+        <v>47.6</v>
       </c>
       <c r="U7" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="V7" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="W7" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>98.8</v>
+        <v>98</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AH7" t="n">
         <v>9</v>
@@ -1670,22 +1737,22 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM7" t="n">
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ7" t="n">
         <v>6</v>
@@ -1700,16 +1767,16 @@
         <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV7" t="n">
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
         <v>8</v>
@@ -1718,13 +1785,13 @@
         <v>10</v>
       </c>
       <c r="BA7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BC7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -1831,25 +1898,25 @@
         <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
         <v>5</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
         <v>13</v>
@@ -1858,10 +1925,10 @@
         <v>22</v>
       </c>
       <c r="AM8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>25</v>
@@ -1882,7 +1949,7 @@
         <v>13</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
         <v>23</v>
@@ -1891,22 +1958,22 @@
         <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
         <v>28</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
         <v>10</v>
@@ -2022,7 +2089,7 @@
         <v>5</v>
       </c>
       <c r="AG9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH9" t="n">
         <v>20</v>
@@ -2034,7 +2101,7 @@
         <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
@@ -2043,19 +2110,19 @@
         <v>23</v>
       </c>
       <c r="AN9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO9" t="n">
         <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ9" t="n">
         <v>9</v>
       </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
         <v>18</v>
@@ -2064,31 +2131,31 @@
         <v>16</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -2117,91 +2184,91 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.357</v>
+        <v>0.385</v>
       </c>
       <c r="H10" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I10" t="n">
         <v>38.2</v>
       </c>
       <c r="J10" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="L10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M10" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N10" t="n">
         <v>0.304</v>
       </c>
       <c r="O10" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="P10" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="R10" t="n">
+        <v>14</v>
+      </c>
+      <c r="S10" t="n">
         <v>29.9</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="R10" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="S10" t="n">
-        <v>29.7</v>
-      </c>
       <c r="T10" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="U10" t="n">
-        <v>20.1</v>
+        <v>19.7</v>
       </c>
       <c r="V10" t="n">
-        <v>15.6</v>
+        <v>15.2</v>
       </c>
       <c r="W10" t="n">
         <v>7.9</v>
       </c>
       <c r="X10" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>25.2</v>
+        <v>25.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>103.3</v>
+        <v>103.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.9</v>
+        <v>-1.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
         <v>23</v>
@@ -2213,22 +2280,22 @@
         <v>4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
         <v>20</v>
       </c>
       <c r="AM10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN10" t="n">
         <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP10" t="n">
         <v>2</v>
@@ -2240,16 +2307,16 @@
         <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
         <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW10" t="n">
         <v>10</v>
@@ -2258,19 +2325,19 @@
         <v>2</v>
       </c>
       <c r="AY10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>3.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF11" t="n">
         <v>5</v>
@@ -2389,7 +2456,7 @@
         <v>5</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI11" t="n">
         <v>28</v>
@@ -2404,13 +2471,13 @@
         <v>13</v>
       </c>
       <c r="AM11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2419,19 +2486,19 @@
         <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS11" t="n">
         <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU11" t="n">
         <v>26</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
         <v>23</v>
@@ -2440,19 +2507,19 @@
         <v>29</v>
       </c>
       <c r="AY11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ11" t="n">
         <v>1</v>
       </c>
       <c r="BA11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
         <v>25</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -2481,91 +2548,91 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.385</v>
+        <v>0.417</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.8</v>
+        <v>37.4</v>
       </c>
       <c r="J12" t="n">
-        <v>83.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.451</v>
+        <v>0.449</v>
       </c>
       <c r="L12" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M12" t="n">
         <v>19.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.357</v>
+        <v>0.361</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="P12" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.774</v>
+        <v>0.771</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="S12" t="n">
         <v>33.8</v>
       </c>
       <c r="T12" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="U12" t="n">
         <v>22</v>
       </c>
       <c r="V12" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="X12" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z12" t="n">
         <v>22.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.2</v>
+        <v>99.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
         <v>22</v>
@@ -2574,49 +2641,49 @@
         <v>7</v>
       </c>
       <c r="AI12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
         <v>8</v>
       </c>
       <c r="AK12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AQ12" t="n">
         <v>12</v>
       </c>
       <c r="AR12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AS12" t="n">
         <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2628,13 +2695,13 @@
         <v>23</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BC12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-9.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2750,16 +2817,16 @@
         <v>29</v>
       </c>
       <c r="AG13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>9</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>10</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
@@ -2768,7 +2835,7 @@
         <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN13" t="n">
         <v>28</v>
@@ -2783,22 +2850,22 @@
         <v>26</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AS13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT13" t="n">
         <v>21</v>
       </c>
       <c r="AU13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV13" t="n">
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX13" t="n">
         <v>4</v>
@@ -2810,7 +2877,7 @@
         <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -2860,70 +2927,70 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="J14" t="n">
-        <v>87.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.46</v>
+        <v>0.457</v>
       </c>
       <c r="L14" t="n">
         <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18</v>
+        <v>17.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.38</v>
+        <v>0.395</v>
       </c>
       <c r="O14" t="n">
-        <v>20.9</v>
+        <v>20.2</v>
       </c>
       <c r="P14" t="n">
-        <v>28.2</v>
+        <v>26.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.743</v>
+        <v>0.759</v>
       </c>
       <c r="R14" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="S14" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="T14" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="U14" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="V14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="W14" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="X14" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.9</v>
+        <v>105.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2941,31 +3008,31 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO14" t="n">
         <v>11</v>
       </c>
-      <c r="AM14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AN14" t="n">
+      <c r="AP14" t="n">
         <v>8</v>
       </c>
-      <c r="AO14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>6</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AR14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
         <v>3</v>
@@ -2974,25 +3041,25 @@
         <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3117,7 +3184,7 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
         <v>29</v>
@@ -3141,7 +3208,7 @@
         <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ15" t="n">
         <v>10</v>
@@ -3150,7 +3217,7 @@
         <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
         <v>13</v>
@@ -3165,16 +3232,16 @@
         <v>9</v>
       </c>
       <c r="AX15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
         <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -3287,28 +3354,28 @@
         <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE16" t="n">
         <v>13</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
         <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AJ16" t="n">
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL16" t="n">
         <v>6</v>
@@ -3320,10 +3387,10 @@
         <v>15</v>
       </c>
       <c r="AO16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
         <v>27</v>
@@ -3332,37 +3399,37 @@
         <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW16" t="n">
         <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY16" t="n">
         <v>3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
         <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>0.467</v>
+        <v>0.438</v>
       </c>
       <c r="H17" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="I17" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J17" t="n">
-        <v>82.5</v>
+        <v>82.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.427</v>
+        <v>0.43</v>
       </c>
       <c r="L17" t="n">
         <v>5.1</v>
@@ -3421,34 +3488,34 @@
         <v>14.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.358</v>
+        <v>0.363</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="P17" t="n">
-        <v>26.5</v>
+        <v>26.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R17" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="S17" t="n">
-        <v>31.9</v>
+        <v>31.1</v>
       </c>
       <c r="T17" t="n">
-        <v>45.6</v>
+        <v>44.8</v>
       </c>
       <c r="U17" t="n">
         <v>20.3</v>
       </c>
       <c r="V17" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="W17" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X17" t="n">
         <v>3.4</v>
@@ -3457,37 +3524,37 @@
         <v>5.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>26</v>
+        <v>26.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>24.3</v>
+        <v>23.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>13</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK17" t="n">
         <v>27</v>
@@ -3499,28 +3566,28 @@
         <v>27</v>
       </c>
       <c r="AN17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS17" t="n">
         <v>13</v>
       </c>
-      <c r="AO17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8</v>
-      </c>
       <c r="AT17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV17" t="n">
         <v>26</v>
@@ -3529,7 +3596,7 @@
         <v>26</v>
       </c>
       <c r="AX17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY17" t="n">
         <v>21</v>
@@ -3541,10 +3608,10 @@
         <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
@@ -3666,13 +3733,13 @@
         <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
         <v>27</v>
@@ -3684,49 +3751,49 @@
         <v>27</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ18" t="n">
         <v>4</v>
       </c>
       <c r="AR18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU18" t="n">
         <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW18" t="n">
         <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY18" t="n">
         <v>23</v>
       </c>
       <c r="AZ18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -3755,145 +3822,145 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>35.2</v>
+        <v>35.6</v>
       </c>
       <c r="J19" t="n">
-        <v>80.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.446</v>
       </c>
       <c r="L19" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M19" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="N19" t="n">
-        <v>0.369</v>
+        <v>0.386</v>
       </c>
       <c r="O19" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="P19" t="n">
-        <v>28.2</v>
+        <v>27.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.777</v>
+        <v>0.769</v>
       </c>
       <c r="R19" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="S19" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T19" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="U19" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="V19" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W19" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="X19" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="AA19" t="n">
         <v>21.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>99.40000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.1</v>
+        <v>-3.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AJ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK19" t="n">
         <v>14</v>
       </c>
-      <c r="AK19" t="n">
-        <v>20</v>
-      </c>
       <c r="AL19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM19" t="n">
         <v>9</v>
       </c>
       <c r="AN19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AO19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AP19" t="n">
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
         <v>22</v>
       </c>
       <c r="AT19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU19" t="n">
         <v>23</v>
       </c>
       <c r="AV19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY19" t="n">
         <v>16</v>
@@ -3902,13 +3969,13 @@
         <v>29</v>
       </c>
       <c r="BA19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BC19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>4.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
         <v>10</v>
@@ -4024,13 +4091,13 @@
         <v>5</v>
       </c>
       <c r="AG20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
@@ -4039,16 +4106,16 @@
         <v>5</v>
       </c>
       <c r="AL20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM20" t="n">
         <v>10</v>
       </c>
-      <c r="AM20" t="n">
-        <v>11</v>
-      </c>
       <c r="AN20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP20" t="n">
         <v>26</v>
@@ -4069,10 +4136,10 @@
         <v>9</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX20" t="n">
         <v>26</v>
@@ -4081,13 +4148,13 @@
         <v>4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA20" t="n">
         <v>20</v>
       </c>
       <c r="BB20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC20" t="n">
         <v>5</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -4119,94 +4186,94 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>0.538</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="J21" t="n">
         <v>87.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.437</v>
+        <v>0.439</v>
       </c>
       <c r="L21" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="M21" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="O21" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P21" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R21" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="S21" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T21" t="n">
         <v>42.2</v>
       </c>
       <c r="U21" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="V21" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="W21" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="X21" t="n">
         <v>1.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>104.9</v>
+        <v>105.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
         <v>13</v>
       </c>
       <c r="AF21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH21" t="n">
         <v>9</v>
@@ -4236,13 +4303,13 @@
         <v>27</v>
       </c>
       <c r="AQ21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT21" t="n">
         <v>12</v>
@@ -4251,16 +4318,16 @@
         <v>3</v>
       </c>
       <c r="AV21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
         <v>5</v>
@@ -4272,7 +4339,7 @@
         <v>2</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -4301,64 +4368,64 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22" t="n">
-        <v>0.067</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="J22" t="n">
-        <v>83.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0.412</v>
       </c>
       <c r="L22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>0.376</v>
+        <v>0.365</v>
       </c>
       <c r="O22" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P22" t="n">
         <v>23.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.77</v>
+        <v>0.762</v>
       </c>
       <c r="R22" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="S22" t="n">
-        <v>31.3</v>
+        <v>31.7</v>
       </c>
       <c r="T22" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="U22" t="n">
-        <v>17.7</v>
+        <v>17</v>
       </c>
       <c r="V22" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W22" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="X22" t="n">
         <v>4.1</v>
@@ -4367,22 +4434,22 @@
         <v>6.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>90.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>-11.5</v>
+        <v>-12.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF22" t="n">
         <v>30</v>
@@ -4409,34 +4476,34 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP22" t="n">
         <v>21</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AT22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>27</v>
       </c>
       <c r="AV22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AX22" t="n">
         <v>24</v>
@@ -4445,10 +4512,10 @@
         <v>27</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB22" t="n">
         <v>29</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>5.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF23" t="n">
         <v>4</v>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI23" t="n">
         <v>22</v>
@@ -4597,7 +4664,7 @@
         <v>6</v>
       </c>
       <c r="AP23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4606,7 +4673,7 @@
         <v>22</v>
       </c>
       <c r="AS23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT23" t="n">
         <v>8</v>
@@ -4615,7 +4682,7 @@
         <v>28</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
         <v>17</v>
@@ -4627,7 +4694,7 @@
         <v>7</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
         <v>5</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -4743,28 +4810,28 @@
         <v>2.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>13</v>
       </c>
       <c r="AF24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
         <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
         <v>28</v>
@@ -4773,13 +4840,13 @@
         <v>28</v>
       </c>
       <c r="AN24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO24" t="n">
         <v>28</v>
       </c>
       <c r="AP24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ24" t="n">
         <v>24</v>
@@ -4791,22 +4858,22 @@
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV24" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AW24" t="n">
         <v>20</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ24" t="n">
         <v>3</v>
@@ -4815,7 +4882,7 @@
         <v>28</v>
       </c>
       <c r="BB24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC24" t="n">
         <v>11</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -4847,55 +4914,55 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F25" t="n">
         <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="H25" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J25" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.499</v>
+        <v>0.497</v>
       </c>
       <c r="L25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="M25" t="n">
-        <v>16.6</v>
+        <v>16.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.386</v>
+        <v>0.382</v>
       </c>
       <c r="O25" t="n">
-        <v>19.7</v>
+        <v>20.2</v>
       </c>
       <c r="P25" t="n">
-        <v>26.6</v>
+        <v>27.4</v>
       </c>
       <c r="Q25" t="n">
         <v>0.739</v>
       </c>
       <c r="R25" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="S25" t="n">
-        <v>31.4</v>
+        <v>31.6</v>
       </c>
       <c r="T25" t="n">
-        <v>39.7</v>
+        <v>40.1</v>
       </c>
       <c r="U25" t="n">
         <v>20.4</v>
@@ -4907,40 +4974,40 @@
         <v>5.9</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.9</v>
+        <v>22.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AC25" t="n">
         <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF25" t="n">
         <v>5</v>
       </c>
       <c r="AG25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AI25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>29</v>
@@ -4949,19 +5016,19 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AP25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ25" t="n">
         <v>25</v>
@@ -4973,10 +5040,10 @@
         <v>11</v>
       </c>
       <c r="AT25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
@@ -4985,22 +5052,22 @@
         <v>29</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA25" t="n">
         <v>7</v>
       </c>
-      <c r="BA25" t="n">
-        <v>10</v>
-      </c>
       <c r="BB25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -5029,58 +5096,58 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
         <v>9</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.643</v>
+        <v>0.6</v>
       </c>
       <c r="H26" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.4</v>
+        <v>35.9</v>
       </c>
       <c r="J26" t="n">
-        <v>79.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.457</v>
+        <v>0.449</v>
       </c>
       <c r="L26" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="N26" t="n">
         <v>0.418</v>
       </c>
       <c r="O26" t="n">
-        <v>18</v>
+        <v>17.3</v>
       </c>
       <c r="P26" t="n">
-        <v>23.4</v>
+        <v>22.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.768</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>26.8</v>
+        <v>27.1</v>
       </c>
       <c r="T26" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="U26" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V26" t="n">
         <v>12.9</v>
@@ -5089,70 +5156,70 @@
         <v>7.9</v>
       </c>
       <c r="X26" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.40000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
         <v>14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
         <v>2</v>
       </c>
       <c r="AO26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP26" t="n">
         <v>23</v>
       </c>
-      <c r="AP26" t="n">
-        <v>22</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
         <v>23</v>
@@ -5164,25 +5231,25 @@
         <v>4</v>
       </c>
       <c r="AW26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX26" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB26" t="n">
         <v>17</v>
       </c>
-      <c r="BA26" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>9</v>
-      </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -5316,10 +5383,10 @@
         <v>22</v>
       </c>
       <c r="AM27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>27</v>
@@ -5352,16 +5419,16 @@
         <v>25</v>
       </c>
       <c r="AY27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ27" t="n">
         <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5538,13 @@
         <v>0.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>13</v>
       </c>
       <c r="AF28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG28" t="n">
         <v>13</v>
@@ -5486,19 +5553,19 @@
         <v>3</v>
       </c>
       <c r="AI28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>5</v>
       </c>
       <c r="AM28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN28" t="n">
         <v>4</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5522,16 +5589,16 @@
         <v>27</v>
       </c>
       <c r="AU28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY28" t="n">
         <v>6</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>-2</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
         <v>19</v>
       </c>
       <c r="AF29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG29" t="n">
         <v>19</v>
@@ -5668,19 +5735,19 @@
         <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL29" t="n">
         <v>12</v>
       </c>
       <c r="AM29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN29" t="n">
         <v>3</v>
@@ -5689,7 +5756,7 @@
         <v>5</v>
       </c>
       <c r="AP29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5701,7 +5768,7 @@
         <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU29" t="n">
         <v>4</v>
@@ -5725,10 +5792,10 @@
         <v>6</v>
       </c>
       <c r="BB29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -5835,28 +5902,28 @@
         <v>2.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
         <v>20</v>
       </c>
       <c r="AI30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL30" t="n">
         <v>29</v>
@@ -5868,37 +5935,37 @@
         <v>20</v>
       </c>
       <c r="AO30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP30" t="n">
         <v>17</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>16</v>
       </c>
       <c r="AQ30" t="n">
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
         <v>24</v>
       </c>
       <c r="AT30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
       </c>
       <c r="AX30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
         <v>19</v>
@@ -5907,10 +5974,10 @@
         <v>8</v>
       </c>
       <c r="BB30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
@@ -5939,157 +6006,157 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>10</v>
       </c>
       <c r="G31" t="n">
-        <v>0.167</v>
+        <v>0.091</v>
       </c>
       <c r="H31" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>36.7</v>
+        <v>35.2</v>
       </c>
       <c r="J31" t="n">
-        <v>82.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.442</v>
+        <v>0.435</v>
       </c>
       <c r="L31" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="M31" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.291</v>
+        <v>0.282</v>
       </c>
       <c r="O31" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="P31" t="n">
-        <v>25.4</v>
+        <v>26.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.748</v>
+        <v>0.75</v>
       </c>
       <c r="R31" t="n">
-        <v>11.7</v>
+        <v>10.6</v>
       </c>
       <c r="S31" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="T31" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="U31" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="V31" t="n">
         <v>13.5</v>
       </c>
       <c r="W31" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="X31" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="Z31" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.9</v>
+        <v>21.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>97.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.1</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF31" t="n">
         <v>26</v>
       </c>
       <c r="AG31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH31" t="n">
         <v>6</v>
       </c>
       <c r="AI31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>12</v>
       </c>
-      <c r="AJ31" t="n">
-        <v>11</v>
-      </c>
       <c r="AK31" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
       </c>
       <c r="AM31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN31" t="n">
         <v>30</v>
       </c>
       <c r="AO31" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AP31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AQ31" t="n">
         <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AS31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT31" t="n">
         <v>25</v>
       </c>
-      <c r="AT31" t="n">
-        <v>22</v>
-      </c>
       <c r="AU31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB31" t="n">
         <v>24</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>19</v>
       </c>
       <c r="BC31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-25-2008-09</t>
+          <t>2008-11-25</t>
         </is>
       </c>
     </row>
